--- a/artfynd/A 44800-2026 artfynd.xlsx
+++ b/artfynd/A 44800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932619</v>
       </c>
       <c r="B2" t="n">
-        <v>108545</v>
+        <v>108547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932620</v>
       </c>
       <c r="B3" t="n">
-        <v>108545</v>
+        <v>108547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932621</v>
       </c>
       <c r="B4" t="n">
-        <v>108545</v>
+        <v>108547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44800-2026 artfynd.xlsx
+++ b/artfynd/A 44800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932619</v>
       </c>
       <c r="B2" t="n">
-        <v>108547</v>
+        <v>108551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932620</v>
       </c>
       <c r="B3" t="n">
-        <v>108547</v>
+        <v>108551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932621</v>
       </c>
       <c r="B4" t="n">
-        <v>108547</v>
+        <v>108551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
